--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T12:07:00+00:00</t>
+    <t>2024-10-03T12:53:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T12:53:10+00:00</t>
+    <t>2024-10-04T13:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T13:17:13+00:00</t>
+    <t>2024-10-04T13:18:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T13:18:14+00:00</t>
+    <t>2024-10-04T16:21:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T16:21:28+00:00</t>
+    <t>2024-10-10T08:55:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-10T08:55:02+00:00</t>
+    <t>2024-10-14T09:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T09:50:56+00:00</t>
+    <t>2024-10-14T11:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T11:03:16+00:00</t>
+    <t>2024-10-14T12:50:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T12:50:57+00:00</t>
+    <t>2024-10-14T13:11:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T13:11:44+00:00</t>
+    <t>2024-10-16T09:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:46:36+00:00</t>
+    <t>2024-10-16T09:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:50:43+00:00</t>
+    <t>2024-10-16T10:26:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:26:24+00:00</t>
+    <t>2024-10-16T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:28:26+00:00</t>
+    <t>2024-10-16T10:32:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:32:07+00:00</t>
+    <t>2024-10-16T11:38:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T11:38:24+00:00</t>
+    <t>2024-10-16T12:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T12:55:09+00:00</t>
+    <t>2024-10-16T13:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T13:04:48+00:00</t>
+    <t>2024-10-17T08:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T08:27:19+00:00</t>
+    <t>2024-10-17T09:21:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T09:21:43+00:00</t>
+    <t>2024-10-17T09:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T09:52:01+00:00</t>
+    <t>2024-10-18T14:48:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T14:48:50+00:00</t>
+    <t>2024-10-18T15:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T15:24:12+00:00</t>
+    <t>2024-10-23T11:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T11:56:44+00:00</t>
+    <t>2024-10-23T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:31:37+00:00</t>
+    <t>2024-10-23T12:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:34:21+00:00</t>
+    <t>2024-10-23T12:43:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:43:26+00:00</t>
+    <t>2024-10-23T12:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:44:55+00:00</t>
+    <t>2024-10-23T12:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/151-modélisation-du-contenu-du-dui-mise-à-jour/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T12:46:34+00:00</t>
+    <t>2024-10-23T13:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
